--- a/TestData/login_data.xlsx
+++ b/TestData/login_data.xlsx
@@ -1,30 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tannu/Study/Automation/Python/PyCharmProjects/Selenium_Pytest_POM/TestData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tannu/Study/Automation/Python/PyCharmProjects/Selenium_Pytest_Hybrid/TestData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37F3176-500D-F547-92C3-0A5162E01340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D17556A-FDBA-BE4E-AB85-B2B9B59C4223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
-    <sheet name="LoginDataDriven" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="24">
-  <si>
-    <t>TestCaseID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>Scenario</t>
   </si>
@@ -38,12 +34,6 @@
     <t>ExpectedResult</t>
   </si>
   <si>
-    <t>ExpectedErrorMessage</t>
-  </si>
-  <si>
-    <t>TC_LOGIN_001</t>
-  </si>
-  <si>
     <t>Valid login</t>
   </si>
   <si>
@@ -56,9 +46,6 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>TC_LOGIN_002</t>
-  </si>
-  <si>
     <t>Invalid password</t>
   </si>
   <si>
@@ -68,31 +55,25 @@
     <t>FAIL</t>
   </si>
   <si>
+    <t>Invalid username</t>
+  </si>
+  <si>
+    <t>WrongUser</t>
+  </si>
+  <si>
+    <t>Blank username</t>
+  </si>
+  <si>
+    <t>Blank password</t>
+  </si>
+  <si>
+    <t>Expected_message</t>
+  </si>
+  <si>
     <t>Invalid credentials</t>
   </si>
   <si>
-    <t>TC_LOGIN_003</t>
-  </si>
-  <si>
-    <t>Invalid username</t>
-  </si>
-  <si>
-    <t>WrongUser</t>
-  </si>
-  <si>
-    <t>TC_LOGIN_004</t>
-  </si>
-  <si>
-    <t>Blank username</t>
-  </si>
-  <si>
     <t>Required</t>
-  </si>
-  <si>
-    <t>TC_LOGIN_005</t>
-  </si>
-  <si>
-    <t>Blank password</t>
   </si>
 </sst>
 </file>
@@ -148,202 +129,120 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Book Antiqua"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Book Antiqua"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Book Antiqua"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Book Antiqua"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Book Antiqua"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Book Antiqua"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Book Antiqua"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -387,28 +286,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LoginDataTable" displayName="LoginDataTable" ref="A1:D6" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="13">
-  <autoFilter ref="A1:D6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="4">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Scenario" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="UserName" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Password" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="ExpectedResult" dataDxfId="9"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9D45C6A-F54A-4B4C-9171-2D10418E5344}" name="LoginDataTable3" displayName="LoginDataTable3" ref="A1:F6" headerRowDxfId="8" dataDxfId="7" totalsRowDxfId="6">
-  <autoFilter ref="A1:F6" xr:uid="{E9D45C6A-F54A-4B4C-9171-2D10418E5344}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7DA98FED-8120-9744-A6BC-D0691F34ADA4}" name="TestCaseID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{B684314C-66F0-054F-B0DB-E5AA2B63175F}" name="Scenario" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{06F2907A-A5C7-674D-BF95-85FBD056C37B}" name="UserName" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{F386108D-C4B4-7247-A660-8EBAE5F9492F}" name="Password" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{4FA552D2-704C-E84E-AEA7-78993353266B}" name="ExpectedResult" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{BB8F2C6F-0EE8-BF4C-B777-989A311249E7}" name="ExpectedErrorMessage" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LoginDataTable" displayName="LoginDataTable" ref="A1:E6" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="6" tableBorderDxfId="7">
+  <autoFilter ref="A1:E6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="5">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Scenario" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="UserName" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Password" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="ExpectedResult" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{47F943C6-E2BC-FD47-9293-387A15A0D7E6}" name="Expected_message" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -699,94 +584,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="1"/>
+    <col min="5" max="5" width="35.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="24" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2"/>
     </row>
-    <row r="2" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="3" spans="1:5" ht="24" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:5" ht="24" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="24" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="24" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -796,139 +698,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32619D3D-ACA7-5D4D-8504-1C7992F3F9A8}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>